--- a/08-design-dynamic/Weapons-James-Gibson-Bond.xlsx
+++ b/08-design-dynamic/Weapons-James-Gibson-Bond.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ariel-gamedev\gamedev-5784\07-design-dynamic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\ariel-gamedev\gamedev-5786\08-design-dynamic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822E57DC-A21C-4543-9682-C7B3C3129D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E844A68-60BA-4155-BFC7-35B60197FE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rules of Play" sheetId="1" r:id="rId1"/>
@@ -200,7 +200,7 @@
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -286,7 +286,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -1031,28 +1031,28 @@
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.6666666666666696</c:v>
+                  <c:v>5.3333333333333357</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.6666666666666696</c:v>
+                  <c:v>5.3333333333333357</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.3333333333333299</c:v>
+                  <c:v>2.6666666666666639</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.3333333333333299</c:v>
+                  <c:v>2.6666666666666639</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.6666666666666698</c:v>
+                  <c:v>1.3333333333333359</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.6666666666666698</c:v>
+                  <c:v>1.3333333333333359</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1272,9 +1272,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1312,7 +1312,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1418,7 +1418,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1560,7 +1560,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1569,24 +1569,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1600,20 +1600,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA7"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.62890625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7890625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7890625" customWidth="1"/>
-    <col min="4" max="4" width="12.3671875" customWidth="1"/>
-    <col min="5" max="5" width="5.26171875" style="2" customWidth="1"/>
-    <col min="6" max="15" width="5.3125" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" style="2" customWidth="1"/>
+    <col min="6" max="15" width="5.33203125" customWidth="1"/>
     <col min="16" max="16" width="5" style="3" customWidth="1"/>
-    <col min="17" max="26" width="5.3125" customWidth="1"/>
+    <col min="17" max="26" width="5.33203125" customWidth="1"/>
     <col min="27" max="27" width="5" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AA1" s="6"/>
     </row>
-    <row r="2" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>1.3333333333333359</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2096,35 +2096,35 @@
       </c>
       <c r="Q7" s="10">
         <f t="shared" si="0"/>
-        <v>6.6666666666666696</v>
+        <v>5.3333333333333357</v>
       </c>
       <c r="R7" s="10">
         <f t="shared" si="0"/>
-        <v>6.6666666666666696</v>
+        <v>5.3333333333333357</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" s="10">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U7" s="10">
         <f t="shared" si="0"/>
-        <v>3.3333333333333299</v>
+        <v>2.6666666666666639</v>
       </c>
       <c r="V7" s="10">
         <f t="shared" si="0"/>
-        <v>3.3333333333333299</v>
+        <v>2.6666666666666639</v>
       </c>
       <c r="W7" s="10">
         <f t="shared" si="0"/>
-        <v>1.6666666666666698</v>
+        <v>1.3333333333333359</v>
       </c>
       <c r="X7" s="10">
         <f t="shared" si="0"/>
-        <v>1.6666666666666698</v>
+        <v>1.3333333333333359</v>
       </c>
       <c r="Y7" s="10">
         <f t="shared" si="0"/>
